--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szaid\OneDrive\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5270866B-8B44-4CCA-B3EA-B61D21087664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6296E7-2F54-4998-9631-5F2921D96987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1128,25 +1128,47 @@
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B9" s="14">
+        <v>400</v>
+      </c>
+      <c r="C9" s="14">
+        <v>70</v>
+      </c>
+      <c r="D9" s="14">
+        <v>50</v>
+      </c>
+      <c r="E9" s="14">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14">
+        <v>4</v>
+      </c>
+      <c r="H9" s="14">
+        <v>55</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>755</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>685</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szaid\OneDrive\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6296E7-2F54-4998-9631-5F2921D96987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9499A46D-213F-4F27-9443-A275E4E0FEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,6 +216,21 @@
   <si>
     <t>MCA</t>
   </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
 </sst>
 </file>
 
@@ -326,7 +341,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -349,11 +364,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -393,6 +419,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -880,74 +909,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12621571</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1172,333 +1201,663 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B10" s="14">
+        <v>400</v>
+      </c>
+      <c r="C10" s="14">
+        <v>50</v>
+      </c>
+      <c r="D10" s="14">
+        <v>60</v>
+      </c>
+      <c r="E10" s="14">
+        <v>40</v>
+      </c>
+      <c r="F10" s="14">
+        <v>160</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>60</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" ref="I10:I69" si="2">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" ref="J10:J69" si="3">IF(I10="","",1440-I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>670</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B11" s="14">
+        <v>350</v>
+      </c>
+      <c r="C11" s="14">
+        <v>40</v>
+      </c>
+      <c r="D11" s="14">
+        <v>30</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>140</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>40</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>810</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B12" s="14">
+        <v>450</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>40</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>130</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>50</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B13" s="14">
+        <v>300</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>60</v>
+      </c>
+      <c r="E13" s="14">
+        <v>15</v>
+      </c>
+      <c r="F13" s="14">
+        <v>170</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>30</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>635</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>805</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B14" s="14">
+        <v>500</v>
+      </c>
+      <c r="C14" s="14">
+        <v>50</v>
+      </c>
+      <c r="D14" s="14">
+        <v>50</v>
+      </c>
+      <c r="E14" s="14">
+        <v>20</v>
+      </c>
+      <c r="F14" s="14">
+        <v>150</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B15" s="14">
+        <v>400</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>30</v>
+      </c>
+      <c r="E15" s="14">
+        <v>40</v>
+      </c>
+      <c r="F15" s="14">
+        <v>180</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>40</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B16" s="14">
+        <v>300</v>
+      </c>
+      <c r="C16" s="14">
+        <v>40</v>
+      </c>
+      <c r="D16" s="14">
+        <v>50</v>
+      </c>
+      <c r="E16" s="14">
+        <v>50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>170</v>
+      </c>
+      <c r="G16" s="14">
+        <v>7</v>
+      </c>
+      <c r="H16" s="14">
+        <v>30</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>800</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B17" s="14">
+        <v>350</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>35</v>
+      </c>
+      <c r="E17" s="14">
+        <v>25</v>
+      </c>
+      <c r="F17" s="14">
+        <v>180</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>35</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>655</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>785</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B18" s="14">
+        <v>380</v>
+      </c>
+      <c r="C18" s="14">
+        <v>40</v>
+      </c>
+      <c r="D18" s="14">
+        <v>45</v>
+      </c>
+      <c r="E18" s="14">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>160</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>55</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B19" s="14">
+        <v>410</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
+      <c r="D19" s="14">
+        <v>40</v>
+      </c>
+      <c r="E19" s="14">
+        <v>40</v>
+      </c>
+      <c r="F19" s="14">
+        <v>150</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>680</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B20" s="14">
+        <v>400</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>50</v>
+      </c>
+      <c r="E20" s="14">
+        <v>45</v>
+      </c>
+      <c r="F20" s="14">
+        <v>170</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>30</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>755</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>685</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14">
+        <v>55</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>160</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>60</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>705</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B22" s="14">
+        <v>380</v>
+      </c>
+      <c r="C22" s="14">
+        <v>50</v>
+      </c>
+      <c r="D22" s="14">
+        <v>60</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>120</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>50</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>750</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="14">
+        <v>340</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>60</v>
+      </c>
+      <c r="E23" s="14">
+        <v>35</v>
+      </c>
+      <c r="F23" s="14">
+        <v>130</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>30</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>655</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>785</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="14">
+        <v>390</v>
+      </c>
+      <c r="C24" s="14">
+        <v>50</v>
+      </c>
+      <c r="D24" s="14">
+        <v>45</v>
+      </c>
+      <c r="E24" s="14">
+        <v>40</v>
+      </c>
+      <c r="F24" s="14">
+        <v>170</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>20</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>715</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>725</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -9810,16 +10169,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+      <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K16 K18:K401 L17" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L20 L22:L401 M21" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
-      <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
